--- a/site/yk_leads.xlsx
+++ b/site/yk_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,12 +570,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Union Mines</t>
+          <t>Dublin Gulch</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>105D 038</t>
+          <t>106D 025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Silver, Lead</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -616,23 +616,23 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U2" t="n">
         <v>35</v>
       </c>
       <c r="V2" t="n">
-        <v>60.31417</v>
+        <v>64.021</v>
       </c>
       <c r="W2" t="n">
-        <v>-135.04083</v>
+        <v>-135.822</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12822</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13910</t>
         </is>
       </c>
     </row>
@@ -642,12 +642,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wheaton Mountain</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>105D 031</t>
+          <t>105D 005</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Copper</t>
+          <t>Gold, Silver, Lead, Zinc, Cadmium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -697,14 +697,14 @@
         <v>35</v>
       </c>
       <c r="V3" t="n">
-        <v>60.25306</v>
+        <v>60.025</v>
       </c>
       <c r="W3" t="n">
-        <v>-135.03667</v>
+        <v>-134.63472</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12816</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12791</t>
         </is>
       </c>
     </row>
@@ -714,24 +714,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tally-Ho</t>
+          <t>Wheaton Mountain</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105D 030</t>
+          <t>105D 031</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Gold</t>
+          <t>Gold, Silver, Lead, Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -769,14 +769,14 @@
         <v>35</v>
       </c>
       <c r="V4" t="n">
-        <v>60.24472</v>
+        <v>60.25306</v>
       </c>
       <c r="W4" t="n">
-        <v>-135.05333</v>
+        <v>-135.03667</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12815</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12816</t>
         </is>
       </c>
     </row>
@@ -786,24 +786,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Union Mines</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>115I 037</t>
+          <t>105D 038</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Zinc, Silver, Gold, Antimony, Lead</t>
+          <t>Gold, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -841,14 +841,14 @@
         <v>35</v>
       </c>
       <c r="V5" t="n">
-        <v>62.42764</v>
+        <v>60.31417</v>
       </c>
       <c r="W5" t="n">
-        <v>-137.6194</v>
+        <v>-135.04083</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14270</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12822</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lone Star</t>
+          <t>Valley</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>115O 072</t>
+          <t>105O 012</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -904,23 +904,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
-        <v>25</v>
+        <v>250</v>
       </c>
       <c r="U6" t="n">
         <v>35</v>
       </c>
       <c r="V6" t="n">
-        <v>63.89194</v>
+        <v>63.628</v>
       </c>
       <c r="W6" t="n">
-        <v>-139.22785</v>
+        <v>-131.295</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14539</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13753</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Big Thing</t>
+          <t>Goddell</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>105D 009</t>
+          <t>105D 025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Gold, Silver, Antimony</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -982,17 +982,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V7" t="n">
-        <v>60.083</v>
+        <v>60.19222</v>
       </c>
       <c r="W7" t="n">
-        <v>-134.687</v>
+        <v>-135.28194</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12794</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12810</t>
         </is>
       </c>
     </row>
@@ -1002,24 +1002,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rex</t>
+          <t>Casino</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>115A 032</t>
+          <t>115J 028</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Copper, Molybdenum, Silver, Gold</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1054,17 +1054,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="V8" t="n">
-        <v>60.73861</v>
+        <v>62.73778</v>
       </c>
       <c r="W8" t="n">
-        <v>-137.30111</v>
+        <v>-138.82806</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14039</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15019</t>
         </is>
       </c>
     </row>
@@ -1074,24 +1074,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Caley</t>
+          <t>Tally-Ho</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>116C 033</t>
+          <t>105D 030</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Copper, Silver, Lead, Gold</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1120,23 +1120,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="V9" t="n">
-        <v>64.30694</v>
+        <v>60.24472</v>
       </c>
       <c r="W9" t="n">
-        <v>-140.19639</v>
+        <v>-135.05333</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14830</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12815</t>
         </is>
       </c>
     </row>
@@ -1146,24 +1146,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kane</t>
+          <t>Inca</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>115A 003</t>
+          <t>105O 015</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1198,17 +1198,377 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
+        <v>34</v>
+      </c>
+      <c r="V10" t="n">
+        <v>63.60556</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-131.95972</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13755</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mount Skukum-Lake Vein</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>105D 158</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Silver, Gold, Arsenic</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Past Producer</t>
+        </is>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>13</v>
+      </c>
+      <c r="T11" t="n">
+        <v>325</v>
+      </c>
+      <c r="U11" t="n">
+        <v>34</v>
+      </c>
+      <c r="V11" t="n">
+        <v>60.21006</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-135.47597</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12942</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Big Thing</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>105D 009</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Silver, Gold</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Past Producer</t>
+        </is>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>13</v>
+      </c>
+      <c r="T12" t="n">
+        <v>325</v>
+      </c>
+      <c r="U12" t="n">
+        <v>34</v>
+      </c>
+      <c r="V12" t="n">
+        <v>60.083</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-134.687</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12794</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Logjam-Main</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>105B 038</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Silver, Gold, Zinc, Lead</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Past Producer</t>
+        </is>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>13</v>
+      </c>
+      <c r="T13" t="n">
+        <v>325</v>
+      </c>
+      <c r="U13" t="n">
+        <v>34</v>
+      </c>
+      <c r="V13" t="n">
+        <v>60.01996</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-131.60149</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12624</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Becker-Cochran</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>105D 027</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Antimony</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Antimony, Gold, Zinc, Nickel, Silver, Copper, Lead</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Past Producer</t>
+        </is>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>12</v>
+      </c>
+      <c r="T14" t="n">
+        <v>300</v>
+      </c>
+      <c r="U14" t="n">
+        <v>32</v>
+      </c>
+      <c r="V14" t="n">
+        <v>60.18472</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-135.215</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12812</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Plata</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>105N 003</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lead, Silver, Gold, Zinc, Cobalt, Copper</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Past Producer</t>
+        </is>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>13</v>
+      </c>
+      <c r="T15" t="n">
+        <v>325</v>
+      </c>
+      <c r="U15" t="n">
         <v>29</v>
       </c>
-      <c r="V10" t="n">
-        <v>60.11361</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-137.13583</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14010</t>
+      <c r="V15" t="n">
+        <v>63.58583</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-132.03194</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13712</t>
         </is>
       </c>
     </row>

--- a/site/yk_leads.xlsx
+++ b/site/yk_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,24 +570,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dublin Gulch</t>
+          <t>Tally-Ho</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>106D 025</t>
+          <t>105D 030</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Silver, Lead, Gold</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -616,23 +616,23 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U2" t="n">
         <v>35</v>
       </c>
       <c r="V2" t="n">
-        <v>64.021</v>
+        <v>60.24472</v>
       </c>
       <c r="W2" t="n">
-        <v>-135.822</v>
+        <v>-135.05333</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13910</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12815</t>
         </is>
       </c>
     </row>
@@ -642,12 +642,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Wheaton Mountain</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>105D 005</t>
+          <t>105D 031</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Cadmium</t>
+          <t>Gold, Silver, Lead, Copper</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -697,14 +697,14 @@
         <v>35</v>
       </c>
       <c r="V3" t="n">
-        <v>60.025</v>
+        <v>60.25306</v>
       </c>
       <c r="W3" t="n">
-        <v>-134.63472</v>
+        <v>-135.03667</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12791</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12816</t>
         </is>
       </c>
     </row>
@@ -714,12 +714,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wheaton Mountain</t>
+          <t>Union Mines</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105D 031</t>
+          <t>105D 038</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Copper</t>
+          <t>Gold, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -769,14 +769,14 @@
         <v>35</v>
       </c>
       <c r="V4" t="n">
-        <v>60.25306</v>
+        <v>60.31417</v>
       </c>
       <c r="W4" t="n">
-        <v>-135.03667</v>
+        <v>-135.04083</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12816</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12822</t>
         </is>
       </c>
     </row>
@@ -786,12 +786,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Union Mines</t>
+          <t>Lone Star</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>105D 038</t>
+          <t>115O 072</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -803,7 +803,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Silver, Lead</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -832,23 +832,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U5" t="n">
         <v>35</v>
       </c>
       <c r="V5" t="n">
-        <v>60.31417</v>
+        <v>63.89194</v>
       </c>
       <c r="W5" t="n">
-        <v>-135.04083</v>
+        <v>-139.22785</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12822</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14539</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Valley</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>105O 012</t>
+          <t>115I 037</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Molybdenum, Zinc, Silver, Gold, Antimony, Lead</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -904,23 +904,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>35</v>
       </c>
       <c r="V6" t="n">
-        <v>63.628</v>
+        <v>62.42764</v>
       </c>
       <c r="W6" t="n">
-        <v>-131.295</v>
+        <v>-137.6194</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13753</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14270</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Goddell</t>
+          <t>Big Thing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>105D 025</t>
+          <t>105D 009</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver, Antimony</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -982,17 +982,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V7" t="n">
-        <v>60.19222</v>
+        <v>60.083</v>
       </c>
       <c r="W7" t="n">
-        <v>-135.28194</v>
+        <v>-134.687</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12810</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12794</t>
         </is>
       </c>
     </row>
@@ -1002,24 +1002,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Casino</t>
+          <t>Rex</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>115J 028</t>
+          <t>115A 032</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1054,17 +1054,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V8" t="n">
-        <v>62.73778</v>
+        <v>60.73861</v>
       </c>
       <c r="W8" t="n">
-        <v>-138.82806</v>
+        <v>-137.30111</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15019</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14039</t>
         </is>
       </c>
     </row>
@@ -1074,24 +1074,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tally-Ho</t>
+          <t>Caley</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>105D 030</t>
+          <t>116C 033</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Gold</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1120,23 +1120,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U9" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V9" t="n">
-        <v>60.24472</v>
+        <v>64.30694</v>
       </c>
       <c r="W9" t="n">
-        <v>-135.05333</v>
+        <v>-140.19639</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12815</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14830</t>
         </is>
       </c>
     </row>
@@ -1146,24 +1146,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Inca</t>
+          <t>Kane</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>105O 015</t>
+          <t>115A 003</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Lead, Silver, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1198,377 +1198,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="V10" t="n">
-        <v>63.60556</v>
+        <v>60.11361</v>
       </c>
       <c r="W10" t="n">
-        <v>-131.95972</v>
+        <v>-137.13583</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13755</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Mount Skukum-Lake Vein</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>105D 158</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Silver, Gold, Arsenic</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="n">
-        <v>13</v>
-      </c>
-      <c r="T11" t="n">
-        <v>325</v>
-      </c>
-      <c r="U11" t="n">
-        <v>34</v>
-      </c>
-      <c r="V11" t="n">
-        <v>60.21006</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-135.47597</v>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12942</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Big Thing</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>105D 009</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Silver, Gold</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I12" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="n">
-        <v>13</v>
-      </c>
-      <c r="T12" t="n">
-        <v>325</v>
-      </c>
-      <c r="U12" t="n">
-        <v>34</v>
-      </c>
-      <c r="V12" t="n">
-        <v>60.083</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-134.687</v>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12794</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Logjam-Main</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>105B 038</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Silver, Gold, Zinc, Lead</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I13" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="n">
-        <v>13</v>
-      </c>
-      <c r="T13" t="n">
-        <v>325</v>
-      </c>
-      <c r="U13" t="n">
-        <v>34</v>
-      </c>
-      <c r="V13" t="n">
-        <v>60.01996</v>
-      </c>
-      <c r="W13" t="n">
-        <v>-131.60149</v>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12624</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Becker-Cochran</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>105D 027</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Antimony</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Antimony, Gold, Zinc, Nickel, Silver, Copper, Lead</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="n">
-        <v>12</v>
-      </c>
-      <c r="T14" t="n">
-        <v>300</v>
-      </c>
-      <c r="U14" t="n">
-        <v>32</v>
-      </c>
-      <c r="V14" t="n">
-        <v>60.18472</v>
-      </c>
-      <c r="W14" t="n">
-        <v>-135.215</v>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12812</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Plata</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>105N 003</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Lead, Silver, Gold, Zinc, Cobalt, Copper</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I15" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="n">
-        <v>13</v>
-      </c>
-      <c r="T15" t="n">
-        <v>325</v>
-      </c>
-      <c r="U15" t="n">
-        <v>29</v>
-      </c>
-      <c r="V15" t="n">
-        <v>63.58583</v>
-      </c>
-      <c r="W15" t="n">
-        <v>-132.03194</v>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13712</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14010</t>
         </is>
       </c>
     </row>
